--- a/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12473</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>21,91%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11345</t>
+          <t>10623</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9014</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20639</t>
+          <t>20918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,48%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43731</t>
+          <t>43527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52265</t>
+          <t>52139</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40026</t>
+          <t>40748</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>48045</t>
+          <t>48065</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>79,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86732</t>
+          <t>86453</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98357</t>
+          <t>98099</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12790</t>
+          <t>13165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26642</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>19236</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35071</t>
+          <t>34629</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>36137</t>
+          <t>35709</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>56787</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283021</t>
+          <t>282722</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>296873</t>
+          <t>296498</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>318565</t>
+          <t>319007</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>334325</t>
+          <t>334400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>605768</t>
+          <t>606512</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>627162</t>
+          <t>627590</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3081</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11732</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5373</t>
+          <t>5138</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,84%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124849</t>
+          <t>125344</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133704</t>
+          <t>133500</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>108758</t>
+          <t>109270</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>118169</t>
+          <t>118404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237622</t>
+          <t>237130</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250221</t>
+          <t>250289</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43683</t>
+          <t>42812</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33619</t>
+          <t>32699</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53681</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61797</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89101</t>
+          <t>88920</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>458560</t>
+          <t>459431</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>476834</t>
+          <t>477324</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>474868</t>
+          <t>475175</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>494930</t>
+          <t>495850</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>89,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>941691</t>
+          <t>941872</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>968995</t>
+          <t>969251</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6558</t>
+          <t>6340</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16335</t>
+          <t>15859</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13959</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13352</t>
+          <t>13777</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26557</t>
+          <t>26650</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39149</t>
+          <t>39625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>48926</t>
+          <t>49144</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>88,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48131</t>
+          <t>48297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>56865</t>
+          <t>57138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91017</t>
+          <t>90924</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>104222</t>
+          <t>103797</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>21830</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39769</t>
+          <t>38086</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24977</t>
+          <t>24511</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43629</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51980</t>
+          <t>52047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76260</t>
+          <t>76114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264884</t>
+          <t>266567</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>283146</t>
+          <t>282823</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>296164</t>
+          <t>294895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>314816</t>
+          <t>315282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>86,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568186</t>
+          <t>568332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>592466</t>
+          <t>592399</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4349</t>
+          <t>4085</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14160</t>
+          <t>13519</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9306</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23412</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,23%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>102667</t>
+          <t>103308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112478</t>
+          <t>112742</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,88%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>123293</t>
+          <t>123556</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133369</t>
+          <t>133511</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230542</t>
+          <t>230313</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244573</t>
+          <t>244419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38389</t>
+          <t>39011</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61454</t>
+          <t>60340</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39493</t>
+          <t>38238</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>62706</t>
+          <t>61357</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83350</t>
+          <t>83051</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114106</t>
+          <t>113810</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>415511</t>
+          <t>416625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>438576</t>
+          <t>437954</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>91,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>476075</t>
+          <t>477424</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>499288</t>
+          <t>500543</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>901640</t>
+          <t>901936</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932396</t>
+          <t>932695</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,82%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4414</t>
+          <t>4288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12566</t>
+          <t>12092</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4376</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10359</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22358</t>
+          <t>21751</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,67%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>28549</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36227</t>
+          <t>36353</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38229</t>
+          <t>37735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47086</t>
+          <t>46861</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>73,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>69520</t>
+          <t>70127</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81519</t>
+          <t>81772</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>89,0%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20466</t>
+          <t>20562</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36622</t>
+          <t>36777</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18900</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43399</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66387</t>
+          <t>66136</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,09%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311394</t>
+          <t>311239</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>327550</t>
+          <t>327454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>343482</t>
+          <t>344808</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>360966</t>
+          <t>361506</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661495</t>
+          <t>661746</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684483</t>
+          <t>684460</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5439</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15477</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7788</t>
+          <t>8241</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8233</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19926</t>
+          <t>19564</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>120550</t>
+          <t>120234</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>130588</t>
+          <t>130693</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>131496</t>
+          <t>131043</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>137943</t>
+          <t>137987</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255385</t>
+          <t>255747</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267078</t>
+          <t>267246</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,76%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34963</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>56558</t>
+          <t>55716</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>28904</t>
+          <t>28628</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>49272</t>
+          <t>48785</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>70008</t>
+          <t>67923</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99045</t>
+          <t>96114</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,78%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>468127</t>
+          <t>468969</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>489722</t>
+          <t>489964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>521115</t>
+          <t>521602</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>541483</t>
+          <t>541759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>996027</t>
+          <t>998958</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1025064</t>
+          <t>1027149</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,8%</t>
         </is>
       </c>
     </row>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9122</t>
+          <t>9227</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10286</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23148</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,33%</t>
+          <t>37,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14475</t>
+          <t>13989</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30738</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44756</t>
+          <t>44651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52025</t>
+          <t>52152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38856</t>
+          <t>38483</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51718</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>85144</t>
+          <t>86503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101407</t>
+          <t>101893</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,47%</t>
+          <t>74,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,93%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19545</t>
+          <t>19521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>37876</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>28694</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53879</t>
+          <t>52562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53731</t>
+          <t>53189</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83605</t>
+          <t>83262</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>419723</t>
+          <t>419997</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>438054</t>
+          <t>438078</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462740</t>
+          <t>464057</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>486195</t>
+          <t>487925</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890613</t>
+          <t>890956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>920487</t>
+          <t>921029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,54%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3857</t>
+          <t>3677</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13446</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2337</t>
+          <t>2417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10958</t>
+          <t>11496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,47 +6278,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>6,33%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>12756</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>7320</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>19859</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>3,88%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2,22%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>12756</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>7385</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>19968</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>3,88%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>6,07%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>134182</t>
+          <t>133949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>143538</t>
+          <t>143718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,51%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170707</t>
+          <t>170169</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179328</t>
+          <t>179248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,47 +6391,47 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>93,67%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>442</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>316304</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>309201</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>321740</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>96,12%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
           <t>93,97%</t>
         </is>
       </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>98,71%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>442</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>316304</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>309092</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>321675</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>96,12%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>93,93%</t>
-        </is>
-      </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29665</t>
+          <t>29421</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>50595</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49592</t>
+          <t>49117</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77792</t>
+          <t>77960</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85282</t>
+          <t>84396</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>119816</t>
+          <t>121118</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>608455</t>
+          <t>608277</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>629207</t>
+          <t>629451</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,35%</t>
+          <t>92,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682496</t>
+          <t>682328</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>710696</t>
+          <t>711171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1299344</t>
+          <t>1298042</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1333878</t>
+          <t>1334764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,05%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/Hacinamiento_R-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6553</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>11360</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>6,51%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>22,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7658</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3861</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12473</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4251</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12729</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>13,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>22,27%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6553</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3306</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10623</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>12,76%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20918</t>
+          <t>21091</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,64%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>44818</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>40011</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>48026</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>87,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>77,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>93,49%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>48342</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43527</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52139</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>43271</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>86,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>77,73%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>44818</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>40748</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>48065</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>87,24%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,32%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86453</t>
+          <t>86280</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98099</t>
+          <t>97842</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>80,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,13%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51371</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>56000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>56000</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>56000</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51371</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26655</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>19494</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35829</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,13%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>19027</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13165</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>26941</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>13506</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>27423</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>6,14%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,7%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26655</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19236</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>34629</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35709</t>
+          <t>35546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56787</t>
+          <t>55867</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>326981</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>317807</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>334142</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,46%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,87%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,49%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>436</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>290636</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>282722</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>296498</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>282240</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>296157</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>93,86%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,3%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,75%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>326981</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>319007</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>334400</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>92,46%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,21%</t>
+          <t>91,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>606512</t>
+          <t>607432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>627590</t>
+          <t>627753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,64%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>532</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>353636</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>464</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>309663</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>309663</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>309663</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>532</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>353636</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8943</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5304</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14971</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>7,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,29%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>6276</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3081</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11237</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11346</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,23%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>8943</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5138</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>14272</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9834</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22993</t>
+          <t>21566</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>114599</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108571</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>118238</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>92,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>87,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>95,71%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>130305</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>125344</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>133500</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>125235</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>133377</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,77%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,74%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>114599</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>109270</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>118404</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>92,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>237130</t>
+          <t>238557</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>250289</t>
+          <t>250738</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,39%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>123542</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136581</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>123542</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42151</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>33274</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>52542</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,3%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,94%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>32961</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>24919</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>42812</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>24916</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>42840</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>6,56%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>4,96%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,52%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>42151</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>32699</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>53374</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>88920</t>
+          <t>88815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>729</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>486398</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>476007</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>495275</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,03%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,06%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,7%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>696</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>469282</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>459431</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>477324</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>459403</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>477327</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>93,44%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,48%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>91,47%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>95,04%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>729</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>486398</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>475175</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>495850</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1425</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>941872</t>
+          <t>941977</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>969251</t>
+          <t>969244</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>744</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>502243</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>502243</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2158,7 +2158,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2326,72 +2326,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8810</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5074</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>14388</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>23,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>10616</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6340</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>15859</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>6631</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>16482</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>19,13%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>11,43%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>28,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>8810</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4952</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13793</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>14,19%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13777</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26650</t>
+          <t>26460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,5%</t>
         </is>
       </c>
     </row>
@@ -2439,72 +2439,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>53280</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47702</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>57016</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>76,83%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,83%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>44868</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>39625</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>49144</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>39002</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>48853</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>80,87%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>88,57%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>53280</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>48297</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>57138</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>85,81%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>70,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90924</t>
+          <t>91114</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>103797</t>
+          <t>104063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>77,33%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -2552,57 +2552,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>62090</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>55484</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>62090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2669,72 +2669,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>24080</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>43136</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>7,09%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>29605</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>21830</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>38086</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>21844</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>39630</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>9,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>7,17%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>12,5%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>33440</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>24511</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>44898</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>9,84%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>52047</t>
+          <t>51779</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>76114</t>
+          <t>76842</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,92%</t>
         </is>
       </c>
     </row>
@@ -2782,74 +2782,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>441</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>306353</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>296657</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>315713</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,16%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87,31%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>92,91%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>399</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>275048</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>266567</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>282823</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>265023</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>282809</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>90,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>87,5%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>86,99%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>92,83%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>441</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>306353</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>294895</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>315282</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,16%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>92,79%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>840</t>
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>568332</t>
+          <t>567604</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>592399</t>
+          <t>592667</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -2895,57 +2895,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>339793</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>441</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>304653</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>487</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>339793</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3012,72 +3012,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7137</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12545</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,48%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,16%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>8269</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>4085</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13519</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>4426</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>13935</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,08%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,57%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7137</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3387</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>13342</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9306</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23412</t>
+          <t>23028</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,08%</t>
         </is>
       </c>
     </row>
@@ -3125,72 +3125,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>129761</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>124353</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>133496</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,79%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,84%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,52%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>155</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>108558</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>103308</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>112742</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>102892</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>112401</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,92%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,43%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,5%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>184</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>129761</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>123556</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>133511</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,79%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>230313</t>
+          <t>230697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>244419</t>
+          <t>244132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -3238,57 +3238,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>136898</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>166</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116827</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>136898</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3360,67 +3360,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>49386</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38616</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>62296</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>7,17%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11,56%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>48489</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>39011</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>60340</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>37802</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>59783</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>10,17%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,65%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>49386</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38238</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61357</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>9,17%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83051</t>
+          <t>84091</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113810</t>
+          <t>114490</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -3468,72 +3468,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>701</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>489395</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>476485</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>500165</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>90,83%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>88,44%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>92,83%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>619</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>428476</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>416625</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>437954</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>417182</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>439163</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>89,83%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>87,35%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>91,82%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>701</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>489395</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>477424</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>500543</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>90,83%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>901936</t>
+          <t>901256</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>932695</t>
+          <t>931655</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -3581,57 +3581,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3750,7 +3750,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3761,7 +3761,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3929,72 +3929,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4195</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12531</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>15,49%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>24,46%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>7637</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>12092</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>12302</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>18,79%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>10,55%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>7935</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>4376</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13502</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>15,49%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10341</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21751</t>
+          <t>21956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,9%</t>
         </is>
       </c>
     </row>
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>43302</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38706</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47042</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>84,51%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>75,54%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>91,81%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>33004</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>28549</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36353</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>28339</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>36628</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>81,21%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>70,25%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>89,45%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>43302</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>37735</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>46861</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>84,51%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>69,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>70127</t>
+          <t>69922</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81772</t>
+          <t>81537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>88,74%</t>
         </is>
       </c>
     </row>
@@ -4155,57 +4155,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>51237</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>40641</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>51237</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4272,72 +4272,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>26155</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>18864</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>35617</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>4,97%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>27436</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>20562</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>36777</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>20240</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>36862</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>7,88%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>10,57%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26155</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>18360</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>35058</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,89%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43422</t>
+          <t>42613</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66136</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -4385,72 +4385,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>508</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>353711</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>344249</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>361002</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>95,03%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>483</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>320580</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>311239</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>327454</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>311154</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>327776</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>92,12%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>89,43%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,09%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>508</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>353711</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>344808</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>361506</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,11%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661746</t>
+          <t>662691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>684460</t>
+          <t>685269</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,15%</t>
         </is>
       </c>
     </row>
@@ -4498,57 +4498,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>544</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>379866</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>348016</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>348016</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>348016</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>379866</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4615,72 +4615,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3655</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1314</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8269</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,62%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>9651</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>5334</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15793</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>5536</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>16307</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>7,09%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>11,61%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>3655</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1297</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>8241</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19564</t>
+          <t>20324</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,38%</t>
         </is>
       </c>
     </row>
@@ -4728,72 +4728,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>135629</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>131015</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>137970</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,38%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>126376</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>120234</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>130693</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>119720</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>130491</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>92,91%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>88,39%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>96,08%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>135629</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>131043</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>137987</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>97,38%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>255747</t>
+          <t>254987</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>267246</t>
+          <t>267278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -4841,57 +4841,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>139284</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139284</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>139284</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>202</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>136027</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>139284</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>139284</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>139284</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4958,72 +4958,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>37745</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28893</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>48170</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>5,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>44723</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>34721</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>55716</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>34354</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>55005</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>8,52%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>37745</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>28628</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48785</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>67923</t>
+          <t>69808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96114</t>
+          <t>97438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -5071,72 +5071,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>532642</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>522217</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>541494</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>93,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,55%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>94,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>479962</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>468969</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>489964</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>469680</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>490331</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>91,48%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>89,38%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>771</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>532642</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>521602</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>541759</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>93,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>93,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>998958</t>
+          <t>997634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1027149</t>
+          <t>1025264</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -5184,57 +5184,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>570387</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>789</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>524685</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>524685</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>570387</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5364,7 +5364,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5532,72 +5532,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>14572</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9188</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20959</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>16,2%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>36,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>4442</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9227</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>17,13%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16642</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>2452</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>23521</t>
+          <t>10190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>37,93%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>21084</t>
+          <t>19888</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>13989</t>
+          <t>13686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29379</t>
+          <t>28823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>28,09%</t>
         </is>
       </c>
     </row>
@@ -5645,72 +5645,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>42160</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>35773</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>47544</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>74,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>63,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>83,8%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>49436</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>44651</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>52152</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>91,75%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>82,87%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>96,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45362</t>
+          <t>40560</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>38483</t>
+          <t>35687</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>43425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>94798</t>
+          <t>82721</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>86503</t>
+          <t>73786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>101893</t>
+          <t>88923</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,65%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -5758,57 +5758,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>68</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53878</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53878</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53878</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>45877</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>102609</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>102609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>102609</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5875,72 +5875,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>36024</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>26478</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>48047</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>10,1%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>27736</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>19521</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>37602</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>27314</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28694</t>
+          <t>19778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52562</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>67684</t>
+          <t>63338</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53189</t>
+          <t>50538</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83262</t>
+          <t>77495</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -5988,72 +5988,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>439654</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>427631</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>449200</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>92,43%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>89,9%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>94,43%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>429863</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>419997</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>438078</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>93,94%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,78%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>95,73%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>476671</t>
+          <t>401530</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464057</t>
+          <t>391754</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>487925</t>
+          <t>409066</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>906534</t>
+          <t>841184</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>890956</t>
+          <t>827027</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>921029</t>
+          <t>853984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -6101,57 +6101,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>640</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>457599</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>457599</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>457599</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>428844</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>428844</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>428844</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>974218</t>
+          <t>904522</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>974218</t>
+          <t>904522</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>974218</t>
+          <t>904522</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6218,72 +6218,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4318</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1906</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8654</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,19%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>7259</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3677</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13446</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>9,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>7007</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2417</t>
+          <t>3777</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11496</t>
+          <t>13325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>12756</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7320</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19859</t>
+          <t>17413</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,54%</t>
         </is>
       </c>
     </row>
@@ -6331,72 +6331,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>162451</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>158115</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>164863</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>97,41%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>94,81%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>140136</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>133949</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>143718</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>90,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,51%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>176169</t>
+          <t>140811</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>170169</t>
+          <t>134493</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>179248</t>
+          <t>144041</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>316304</t>
+          <t>303263</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>309201</t>
+          <t>297174</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>321740</t>
+          <t>307438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -6444,57 +6444,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166769</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166769</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166769</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>147395</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>147395</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>147395</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181665</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181665</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181665</t>
+          <t>147818</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>329060</t>
+          <t>314587</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>329060</t>
+          <t>314587</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>329060</t>
+          <t>314587</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6561,72 +6561,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>54913</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42903</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>69325</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7,85%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6,14%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>39438</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29421</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>50595</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5,99%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4,47%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>39637</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>30947</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>77960</t>
+          <t>50229</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,17 +6636,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>101524</t>
+          <t>94550</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84396</t>
+          <t>79613</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121118</t>
+          <t>113201</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -6674,72 +6674,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>644266</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>629854</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>656276</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>92,15%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>90,08%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>93,86%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>873</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>619434</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>608277</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>629451</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>94,01%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>92,32%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>95,53%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>896</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>698202</t>
+          <t>582902</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>682328</t>
+          <t>572310</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>711171</t>
+          <t>591592</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,17 +6749,17 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1317636</t>
+          <t>1227168</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1298042</t>
+          <t>1208517</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1334764</t>
+          <t>1242105</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,98%</t>
         </is>
       </c>
     </row>
@@ -6787,57 +6787,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>974</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>699179</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>935</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>658872</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>658872</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>658872</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>974</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>622539</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>622539</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>760288</t>
+          <t>622539</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1419160</t>
+          <t>1321718</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1419160</t>
+          <t>1321718</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1419160</t>
+          <t>1321718</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
